--- a/Sindhi Muslim/Classes/4-9 GBPS Data for Software.xlsx
+++ b/Sindhi Muslim/Classes/4-9 GBPS Data for Software.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044701C0-2F53-4F84-A812-9E3AEDD24DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C015503-A7AA-4F8E-9E3D-46BA440C645B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2296" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="767">
   <si>
     <t>STUDENT PROFILE 2024-2025</t>
   </si>
@@ -1894,9 +1894,6 @@
     <t>Abdul Salam</t>
   </si>
   <si>
-    <t>Ameer Ali</t>
-  </si>
-  <si>
     <t>Faizan Ali</t>
   </si>
   <si>
@@ -2222,6 +2219,123 @@
   </si>
   <si>
     <t>43203-7544021-3</t>
+  </si>
+  <si>
+    <t>42201-0586713-2</t>
+  </si>
+  <si>
+    <t>0314-1303560</t>
+  </si>
+  <si>
+    <t>42501-9055849-0</t>
+  </si>
+  <si>
+    <t>0340-0361447</t>
+  </si>
+  <si>
+    <t>45303-500755-3</t>
+  </si>
+  <si>
+    <t>0314-3503891</t>
+  </si>
+  <si>
+    <t>42501-1487621-5</t>
+  </si>
+  <si>
+    <t>0309-2646156</t>
+  </si>
+  <si>
+    <t>41201-5264863-7</t>
+  </si>
+  <si>
+    <t>0347-9539690</t>
+  </si>
+  <si>
+    <t>43103-3592618-5</t>
+  </si>
+  <si>
+    <t>0328-268358</t>
+  </si>
+  <si>
+    <t>42501-5630707-0</t>
+  </si>
+  <si>
+    <t>0300-086705</t>
+  </si>
+  <si>
+    <t>42201-6810117-1</t>
+  </si>
+  <si>
+    <t>0317-0373515</t>
+  </si>
+  <si>
+    <t>34603-8946412-7</t>
+  </si>
+  <si>
+    <t>0307-2886358</t>
+  </si>
+  <si>
+    <t>53404-9960541-7</t>
+  </si>
+  <si>
+    <t>45303-5007552-3</t>
+  </si>
+  <si>
+    <t>42501-4584929-3</t>
+  </si>
+  <si>
+    <t>Amir Ali</t>
+  </si>
+  <si>
+    <t>43205-9597118-1</t>
+  </si>
+  <si>
+    <t>0346-3359514</t>
+  </si>
+  <si>
+    <t>0317-294747</t>
+  </si>
+  <si>
+    <t>42501-6369083-9</t>
+  </si>
+  <si>
+    <t>43105-4788357-9</t>
+  </si>
+  <si>
+    <t>0315-8216489</t>
+  </si>
+  <si>
+    <t>43105-3452340-1</t>
+  </si>
+  <si>
+    <t>42000-0869454-9</t>
+  </si>
+  <si>
+    <t>0314-1708363</t>
+  </si>
+  <si>
+    <t>42501-1171541-3</t>
+  </si>
+  <si>
+    <t>0335-2804279</t>
+  </si>
+  <si>
+    <t>42201-3536355-6</t>
+  </si>
+  <si>
+    <t>0311-2563356</t>
+  </si>
+  <si>
+    <t>43303-4558737-3</t>
+  </si>
+  <si>
+    <t>0334-3850237</t>
+  </si>
+  <si>
+    <t>45206-6028202-5</t>
+  </si>
+  <si>
+    <t>0305-3718171</t>
   </si>
 </sst>
 </file>
@@ -2231,12 +2345,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2461,18 +2582,12 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -2572,119 +2687,245 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="59">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3178,25 +3419,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="46"/>
-      <tableStyleElement type="headerRow" dxfId="45"/>
-      <tableStyleElement type="totalRow" dxfId="44"/>
-      <tableStyleElement type="firstColumn" dxfId="43"/>
-      <tableStyleElement type="lastColumn" dxfId="42"/>
-      <tableStyleElement type="firstRowStripe" dxfId="41"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="40"/>
+      <tableStyleElement type="wholeTable" dxfId="58"/>
+      <tableStyleElement type="headerRow" dxfId="57"/>
+      <tableStyleElement type="totalRow" dxfId="56"/>
+      <tableStyleElement type="firstColumn" dxfId="55"/>
+      <tableStyleElement type="lastColumn" dxfId="54"/>
+      <tableStyleElement type="firstRowStripe" dxfId="53"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="52"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="39"/>
-      <tableStyleElement type="totalRow" dxfId="38"/>
-      <tableStyleElement type="firstRowStripe" dxfId="37"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="36"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="35"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="34"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="33"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="32"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="31"/>
-      <tableStyleElement type="pageFieldValues" dxfId="30"/>
+      <tableStyleElement type="headerRow" dxfId="51"/>
+      <tableStyleElement type="totalRow" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="48"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="47"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="46"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="45"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="44"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="43"/>
+      <tableStyleElement type="pageFieldValues" dxfId="42"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3550,173 +3791,173 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="72" customFormat="1" ht="15.75">
-      <c r="A3" s="63">
+    <row r="3" spans="1:14" s="76" customFormat="1" ht="15.75">
+      <c r="A3" s="67">
         <v>1</v>
       </c>
-      <c r="B3" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="65">
+      <c r="B3" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="69">
         <v>527</v>
       </c>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="70" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="H3" s="68">
+      <c r="H3" s="72">
         <v>42358</v>
       </c>
-      <c r="I3" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="J3" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="K3" s="68">
+      <c r="I3" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="K3" s="72">
         <v>44441</v>
       </c>
-      <c r="L3" s="70" t="s">
+      <c r="L3" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="M3" s="71"/>
-      <c r="N3" s="71" t="s">
+      <c r="M3" s="75"/>
+      <c r="N3" s="75" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="72" customFormat="1" ht="15.75">
-      <c r="A4" s="63">
+    <row r="4" spans="1:14" s="76" customFormat="1" ht="15.75">
+      <c r="A4" s="67">
         <v>2</v>
       </c>
-      <c r="B4" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="73">
+      <c r="B4" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="77">
         <v>472</v>
       </c>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="68">
+      <c r="H4" s="72">
         <v>41647</v>
       </c>
-      <c r="I4" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="J4" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="K4" s="68">
+      <c r="I4" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="J4" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="K4" s="72">
         <v>44814</v>
       </c>
-      <c r="L4" s="70" t="s">
+      <c r="L4" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="M4" s="71" t="s">
-        <v>705</v>
-      </c>
-      <c r="N4" s="71" t="s">
+      <c r="M4" s="75" t="s">
+        <v>704</v>
+      </c>
+      <c r="N4" s="75" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="72" customFormat="1" ht="15.75">
-      <c r="A5" s="63">
+    <row r="5" spans="1:14" s="76" customFormat="1" ht="15.75">
+      <c r="A5" s="67">
         <v>3</v>
       </c>
-      <c r="B5" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="73">
+      <c r="B5" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="77">
         <v>549</v>
       </c>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="72">
         <v>42005</v>
       </c>
-      <c r="I5" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="J5" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="K5" s="68">
+      <c r="I5" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="J5" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="72">
         <v>44356</v>
       </c>
-      <c r="L5" s="70" t="s">
+      <c r="L5" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71" t="s">
+      <c r="M5" s="75"/>
+      <c r="N5" s="75" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:14" s="72" customFormat="1" ht="15.75">
-      <c r="A6" s="63">
+    <row r="6" spans="1:14" s="76" customFormat="1" ht="15.75">
+      <c r="A6" s="67">
         <v>4</v>
       </c>
-      <c r="B6" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="73">
+      <c r="B6" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="77">
         <v>405</v>
       </c>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="64" t="s">
+      <c r="F6" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="68" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="68">
+      <c r="H6" s="72">
         <v>41558</v>
       </c>
-      <c r="I6" s="69" t="s">
-        <v>117</v>
-      </c>
-      <c r="J6" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="K6" s="68">
+      <c r="I6" s="73" t="s">
+        <v>117</v>
+      </c>
+      <c r="J6" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" s="72">
         <v>43381</v>
       </c>
-      <c r="L6" s="70" t="s">
+      <c r="L6" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71" t="s">
+      <c r="M6" s="75"/>
+      <c r="N6" s="75" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4333,7 +4574,7 @@
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="12" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>52</v>
@@ -4389,10 +4630,10 @@
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="60" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>126</v>
@@ -4473,10 +4714,10 @@
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="60" t="s">
+        <v>695</v>
+      </c>
+      <c r="M25" s="7" t="s">
         <v>696</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>697</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>126</v>
@@ -4515,10 +4756,10 @@
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="60" t="s">
+        <v>697</v>
+      </c>
+      <c r="M26" s="7" t="s">
         <v>698</v>
-      </c>
-      <c r="M26" s="7" t="s">
-        <v>699</v>
       </c>
       <c r="N26" s="7" t="s">
         <v>126</v>
@@ -4557,10 +4798,10 @@
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="60" t="s">
+        <v>699</v>
+      </c>
+      <c r="M27" s="7" t="s">
         <v>700</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>701</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>126</v>
@@ -4599,7 +4840,7 @@
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="60" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M28" s="7" t="s">
         <v>422</v>
@@ -4641,10 +4882,10 @@
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="60" t="s">
+        <v>702</v>
+      </c>
+      <c r="M29" s="7" t="s">
         <v>703</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>704</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>126</v>
@@ -4686,7 +4927,7 @@
         <v>122</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="N30" s="7" t="s">
         <v>126</v>
@@ -4725,10 +4966,10 @@
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="60" t="s">
+        <v>705</v>
+      </c>
+      <c r="M31" s="7" t="s">
         <v>706</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>707</v>
       </c>
       <c r="N31" s="7" t="s">
         <v>126</v>
@@ -4803,10 +5044,10 @@
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="60" t="s">
+        <v>705</v>
+      </c>
+      <c r="M33" s="60" t="s">
         <v>706</v>
-      </c>
-      <c r="M33" s="60" t="s">
-        <v>707</v>
       </c>
       <c r="N33" s="7" t="s">
         <v>126</v>
@@ -4890,7 +5131,7 @@
         <v>365</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="N35" s="7" t="s">
         <v>126</v>
@@ -4929,10 +5170,10 @@
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="60" t="s">
+        <v>708</v>
+      </c>
+      <c r="M36" s="7" t="s">
         <v>709</v>
-      </c>
-      <c r="M36" s="7" t="s">
-        <v>710</v>
       </c>
       <c r="N36" s="7" t="s">
         <v>126</v>
@@ -5015,7 +5256,7 @@
         <v>43807</v>
       </c>
       <c r="L38" s="60" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M38" s="38" t="s">
         <v>224</v>
@@ -5099,10 +5340,10 @@
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="60" t="s">
+        <v>711</v>
+      </c>
+      <c r="M40" s="60" t="s">
         <v>712</v>
-      </c>
-      <c r="M40" s="60" t="s">
-        <v>713</v>
       </c>
       <c r="N40" s="7" t="s">
         <v>126</v>
@@ -5141,10 +5382,10 @@
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="60" t="s">
+        <v>713</v>
+      </c>
+      <c r="M41" s="60" t="s">
         <v>714</v>
-      </c>
-      <c r="M41" s="60" t="s">
-        <v>715</v>
       </c>
       <c r="N41" s="7" t="s">
         <v>126</v>
@@ -5225,7 +5466,7 @@
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="60" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>451</v>
@@ -5349,10 +5590,10 @@
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="60" t="s">
+        <v>716</v>
+      </c>
+      <c r="M46" s="7" t="s">
         <v>717</v>
-      </c>
-      <c r="M46" s="7" t="s">
-        <v>718</v>
       </c>
       <c r="N46" s="7" t="s">
         <v>126</v>
@@ -5433,7 +5674,7 @@
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="60" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M48" s="7"/>
       <c r="N48" s="7" t="s">
@@ -5515,10 +5756,10 @@
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="60" t="s">
+        <v>718</v>
+      </c>
+      <c r="M50" s="7" t="s">
         <v>719</v>
-      </c>
-      <c r="M50" s="7" t="s">
-        <v>720</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>126</v>
@@ -5557,10 +5798,10 @@
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="60" t="s">
+        <v>720</v>
+      </c>
+      <c r="M51" s="7" t="s">
         <v>721</v>
-      </c>
-      <c r="M51" s="7" t="s">
-        <v>722</v>
       </c>
       <c r="N51" s="7" t="s">
         <v>126</v>
@@ -5646,7 +5887,7 @@
         <v>385</v>
       </c>
       <c r="M53" s="60" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="N53" s="7" t="s">
         <v>126</v>
@@ -5685,10 +5926,10 @@
       </c>
       <c r="K54" s="16"/>
       <c r="L54" s="60" t="s">
+        <v>723</v>
+      </c>
+      <c r="M54" s="60" t="s">
         <v>724</v>
-      </c>
-      <c r="M54" s="60" t="s">
-        <v>725</v>
       </c>
       <c r="N54" s="7" t="s">
         <v>126</v>
@@ -5725,10 +5966,10 @@
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="60" t="s">
+        <v>725</v>
+      </c>
+      <c r="M55" s="60" t="s">
         <v>726</v>
-      </c>
-      <c r="M55" s="60" t="s">
-        <v>727</v>
       </c>
       <c r="N55" s="7" t="s">
         <v>126</v>
@@ -10721,10 +10962,10 @@
       </c>
       <c r="K181" s="16"/>
       <c r="L181" s="51" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="M181" s="51" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="N181" s="7"/>
     </row>
@@ -10801,7 +11042,7 @@
       </c>
       <c r="K183" s="16"/>
       <c r="L183" s="51" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="M183" s="51" t="s">
         <v>238</v>
@@ -10844,7 +11085,7 @@
         <v>237</v>
       </c>
       <c r="M184" s="51" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="N184" s="7"/>
     </row>
@@ -10881,10 +11122,10 @@
       </c>
       <c r="K185" s="16"/>
       <c r="L185" s="56" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="M185" s="56" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="N185" s="7"/>
     </row>
@@ -10959,10 +11200,10 @@
       </c>
       <c r="K187" s="16"/>
       <c r="L187" s="56" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="M187" s="56" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="N187" s="7"/>
     </row>
@@ -11000,7 +11241,7 @@
       <c r="K188" s="16"/>
       <c r="L188" s="38"/>
       <c r="M188" s="56" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="N188" s="7"/>
     </row>
@@ -11069,10 +11310,10 @@
       </c>
       <c r="K190" s="16"/>
       <c r="L190" s="56" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="M190" s="56" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N190" s="7"/>
     </row>
@@ -11109,7 +11350,7 @@
       </c>
       <c r="K191" s="16"/>
       <c r="L191" s="56" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="M191" s="56" t="s">
         <v>278</v>
@@ -11188,7 +11429,7 @@
       <c r="K193" s="16"/>
       <c r="L193" s="38"/>
       <c r="M193" s="56" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="N193" s="7"/>
     </row>
@@ -11305,10 +11546,10 @@
       </c>
       <c r="K196" s="16"/>
       <c r="L196" s="57" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="M196" s="57" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="N196" s="7"/>
     </row>
@@ -11345,10 +11586,10 @@
       </c>
       <c r="K197" s="16"/>
       <c r="L197" s="57" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="M197" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N197" s="7"/>
     </row>
@@ -11385,10 +11626,10 @@
       </c>
       <c r="K198" s="16"/>
       <c r="L198" s="57" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="M198" s="57" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="N198" s="7"/>
     </row>
@@ -11425,7 +11666,7 @@
       </c>
       <c r="K199" s="16"/>
       <c r="L199" s="57" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M199" s="14"/>
       <c r="N199" s="7"/>
@@ -11463,10 +11704,10 @@
       </c>
       <c r="K200" s="16"/>
       <c r="L200" s="57" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="M200" s="57" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="N200" s="7"/>
     </row>
@@ -11543,10 +11784,10 @@
       </c>
       <c r="K202" s="29"/>
       <c r="L202" s="57" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="M202" s="57" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="N202" s="7"/>
     </row>
@@ -11623,10 +11864,10 @@
       </c>
       <c r="K204" s="16"/>
       <c r="L204" s="57" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M204" s="57" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="N204" s="7"/>
     </row>
@@ -11661,10 +11902,10 @@
       </c>
       <c r="K205" s="16"/>
       <c r="L205" s="57" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="M205" s="57" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="N205" s="7"/>
     </row>
@@ -11701,7 +11942,7 @@
       </c>
       <c r="K206" s="16"/>
       <c r="L206" s="57" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="M206" s="57" t="s">
         <v>443</v>
@@ -11744,7 +11985,7 @@
         <v>393</v>
       </c>
       <c r="M207" s="57" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N207" s="7"/>
     </row>
@@ -11851,10 +12092,10 @@
       </c>
       <c r="K210" s="16"/>
       <c r="L210" s="57" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="M210" s="57" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="N210" s="7"/>
     </row>
@@ -11891,7 +12132,7 @@
       </c>
       <c r="K211" s="16"/>
       <c r="L211" s="57" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="M211" s="57" t="s">
         <v>235</v>
@@ -11931,10 +12172,10 @@
       </c>
       <c r="K212" s="16"/>
       <c r="L212" s="57" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="M212" s="57" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="N212" s="7"/>
     </row>
@@ -11971,10 +12212,10 @@
       </c>
       <c r="K213" s="16"/>
       <c r="L213" s="57" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="M213" s="57" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="N213" s="7"/>
     </row>
@@ -12041,10 +12282,10 @@
       </c>
       <c r="K215" s="16"/>
       <c r="L215" s="57" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="M215" s="57" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="N215" s="7"/>
     </row>
@@ -12081,10 +12322,10 @@
       </c>
       <c r="K216" s="16"/>
       <c r="L216" s="59" t="s">
+        <v>682</v>
+      </c>
+      <c r="M216" s="59" t="s">
         <v>683</v>
-      </c>
-      <c r="M216" s="59" t="s">
-        <v>684</v>
       </c>
       <c r="N216" s="7"/>
     </row>
@@ -12121,10 +12362,10 @@
       </c>
       <c r="K217" s="16"/>
       <c r="L217" s="59" t="s">
+        <v>684</v>
+      </c>
+      <c r="M217" s="59" t="s">
         <v>685</v>
-      </c>
-      <c r="M217" s="59" t="s">
-        <v>686</v>
       </c>
       <c r="N217" s="7"/>
     </row>
@@ -12161,10 +12402,10 @@
       </c>
       <c r="K218" s="16"/>
       <c r="L218" s="59" t="s">
+        <v>686</v>
+      </c>
+      <c r="M218" s="59" t="s">
         <v>687</v>
-      </c>
-      <c r="M218" s="59" t="s">
-        <v>688</v>
       </c>
       <c r="N218" s="7"/>
     </row>
@@ -12201,10 +12442,10 @@
       </c>
       <c r="K219" s="16"/>
       <c r="L219" s="59" t="s">
+        <v>688</v>
+      </c>
+      <c r="M219" s="59" t="s">
         <v>689</v>
-      </c>
-      <c r="M219" s="59" t="s">
-        <v>690</v>
       </c>
       <c r="N219" s="7"/>
     </row>
@@ -12281,10 +12522,10 @@
       </c>
       <c r="K221" s="16"/>
       <c r="L221" s="59" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="M221" s="59" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="N221" s="7"/>
     </row>
@@ -12321,10 +12562,10 @@
       </c>
       <c r="K222" s="31"/>
       <c r="L222" s="57" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M222" s="57" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="N222" s="7"/>
     </row>
@@ -12332,7 +12573,7 @@
       <c r="A223" s="14">
         <v>224</v>
       </c>
-      <c r="B223" s="33" t="s">
+      <c r="B223" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C223" s="50">
@@ -12344,29 +12585,35 @@
       <c r="E223" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="F223" s="41" t="s">
+      <c r="F223" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G223" s="51" t="s">
+      <c r="G223" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H223" s="16"/>
-      <c r="I223" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J223" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K223" s="16"/>
-      <c r="L223" s="38"/>
-      <c r="M223" s="20"/>
+      <c r="H223" s="64">
+        <v>40248</v>
+      </c>
+      <c r="I223" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J223" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K223" s="64"/>
+      <c r="L223" s="63" t="s">
+        <v>728</v>
+      </c>
+      <c r="M223" s="63" t="s">
+        <v>729</v>
+      </c>
       <c r="N223" s="7"/>
     </row>
     <row r="224" spans="1:14" ht="15.75">
       <c r="A224" s="14">
         <v>225</v>
       </c>
-      <c r="B224" s="33" t="s">
+      <c r="B224" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C224" s="50">
@@ -12378,29 +12625,35 @@
       <c r="E224" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="F224" s="41" t="s">
+      <c r="F224" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G224" s="51" t="s">
+      <c r="G224" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H224" s="16"/>
-      <c r="I224" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J224" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K224" s="16"/>
-      <c r="L224" s="38"/>
-      <c r="M224" s="14"/>
+      <c r="H224" s="64">
+        <v>39839</v>
+      </c>
+      <c r="I224" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J224" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K224" s="64"/>
+      <c r="L224" s="63" t="s">
+        <v>730</v>
+      </c>
+      <c r="M224" s="63" t="s">
+        <v>731</v>
+      </c>
       <c r="N224" s="7"/>
     </row>
     <row r="225" spans="1:14" ht="15.75">
       <c r="A225" s="14">
         <v>226</v>
       </c>
-      <c r="B225" s="33" t="s">
+      <c r="B225" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C225" s="50">
@@ -12412,29 +12665,35 @@
       <c r="E225" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="F225" s="41" t="s">
+      <c r="F225" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G225" s="51" t="s">
+      <c r="G225" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H225" s="16"/>
-      <c r="I225" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J225" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K225" s="16"/>
-      <c r="L225" s="38"/>
-      <c r="M225" s="20"/>
+      <c r="H225" s="64">
+        <v>41325</v>
+      </c>
+      <c r="I225" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J225" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K225" s="64"/>
+      <c r="L225" s="63" t="s">
+        <v>732</v>
+      </c>
+      <c r="M225" s="63" t="s">
+        <v>733</v>
+      </c>
       <c r="N225" s="7"/>
     </row>
     <row r="226" spans="1:14" ht="15.75">
       <c r="A226" s="14">
         <v>227</v>
       </c>
-      <c r="B226" s="33" t="s">
+      <c r="B226" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C226" s="50">
@@ -12446,29 +12705,35 @@
       <c r="E226" s="13" t="s">
         <v>563</v>
       </c>
-      <c r="F226" s="41" t="s">
+      <c r="F226" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G226" s="51" t="s">
+      <c r="G226" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H226" s="16"/>
-      <c r="I226" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J226" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K226" s="16"/>
-      <c r="L226" s="38"/>
-      <c r="M226" s="14"/>
+      <c r="H226" s="64">
+        <v>40782</v>
+      </c>
+      <c r="I226" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J226" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K226" s="64"/>
+      <c r="L226" s="63" t="s">
+        <v>679</v>
+      </c>
+      <c r="M226" s="63" t="s">
+        <v>650</v>
+      </c>
       <c r="N226" s="7"/>
     </row>
     <row r="227" spans="1:14" ht="15.75">
       <c r="A227" s="14">
         <v>228</v>
       </c>
-      <c r="B227" s="33" t="s">
+      <c r="B227" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C227" s="50">
@@ -12480,29 +12745,35 @@
       <c r="E227" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F227" s="41" t="s">
+      <c r="F227" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G227" s="51" t="s">
+      <c r="G227" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H227" s="16"/>
-      <c r="I227" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J227" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K227" s="16"/>
-      <c r="L227" s="38"/>
-      <c r="M227" s="20"/>
+      <c r="H227" s="64">
+        <v>38967</v>
+      </c>
+      <c r="I227" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J227" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K227" s="64"/>
+      <c r="L227" s="63" t="s">
+        <v>582</v>
+      </c>
+      <c r="M227" s="63" t="s">
+        <v>466</v>
+      </c>
       <c r="N227" s="7"/>
     </row>
     <row r="228" spans="1:14" ht="15.75">
       <c r="A228" s="14">
         <v>229</v>
       </c>
-      <c r="B228" s="33" t="s">
+      <c r="B228" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C228" s="50">
@@ -12514,29 +12785,35 @@
       <c r="E228" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="F228" s="41" t="s">
+      <c r="F228" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G228" s="51" t="s">
+      <c r="G228" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H228" s="16"/>
-      <c r="I228" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J228" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K228" s="16"/>
-      <c r="L228" s="38"/>
-      <c r="M228" s="7"/>
+      <c r="H228" s="64">
+        <v>39787</v>
+      </c>
+      <c r="I228" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J228" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K228" s="64"/>
+      <c r="L228" s="63" t="s">
+        <v>124</v>
+      </c>
+      <c r="M228" s="63" t="s">
+        <v>729</v>
+      </c>
       <c r="N228" s="7"/>
     </row>
     <row r="229" spans="1:14" ht="15.75">
       <c r="A229" s="14">
         <v>230</v>
       </c>
-      <c r="B229" s="33" t="s">
+      <c r="B229" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C229" s="50">
@@ -12548,29 +12825,35 @@
       <c r="E229" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="F229" s="41" t="s">
+      <c r="F229" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G229" s="51" t="s">
+      <c r="G229" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H229" s="16"/>
-      <c r="I229" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J229" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K229" s="16"/>
-      <c r="L229" s="38"/>
-      <c r="M229" s="28"/>
+      <c r="H229" s="64">
+        <v>40725</v>
+      </c>
+      <c r="I229" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J229" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K229" s="64"/>
+      <c r="L229" s="63" t="s">
+        <v>407</v>
+      </c>
+      <c r="M229" s="63" t="s">
+        <v>408</v>
+      </c>
       <c r="N229" s="7"/>
     </row>
     <row r="230" spans="1:14" ht="15.75">
       <c r="A230" s="14">
         <v>231</v>
       </c>
-      <c r="B230" s="33" t="s">
+      <c r="B230" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C230" s="50">
@@ -12582,29 +12865,35 @@
       <c r="E230" s="13" t="s">
         <v>595</v>
       </c>
-      <c r="F230" s="41" t="s">
+      <c r="F230" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G230" s="51" t="s">
+      <c r="G230" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H230" s="16"/>
-      <c r="I230" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J230" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K230" s="16"/>
-      <c r="L230" s="38"/>
-      <c r="M230" s="20"/>
+      <c r="H230" s="64">
+        <v>40683</v>
+      </c>
+      <c r="I230" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J230" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K230" s="64"/>
+      <c r="L230" s="63" t="s">
+        <v>734</v>
+      </c>
+      <c r="M230" s="63" t="s">
+        <v>735</v>
+      </c>
       <c r="N230" s="7"/>
     </row>
     <row r="231" spans="1:14" ht="15.75">
       <c r="A231" s="14">
         <v>232</v>
       </c>
-      <c r="B231" s="33" t="s">
+      <c r="B231" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C231" s="50">
@@ -12616,29 +12905,35 @@
       <c r="E231" s="13" t="s">
         <v>597</v>
       </c>
-      <c r="F231" s="41" t="s">
+      <c r="F231" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G231" s="51" t="s">
+      <c r="G231" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H231" s="16"/>
-      <c r="I231" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J231" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K231" s="16"/>
-      <c r="L231" s="38"/>
-      <c r="M231" s="14"/>
+      <c r="H231" s="64">
+        <v>39943</v>
+      </c>
+      <c r="I231" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J231" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K231" s="64"/>
+      <c r="L231" s="63" t="s">
+        <v>702</v>
+      </c>
+      <c r="M231" s="63" t="s">
+        <v>703</v>
+      </c>
       <c r="N231" s="7"/>
     </row>
     <row r="232" spans="1:14" ht="15.75">
       <c r="A232" s="14">
         <v>233</v>
       </c>
-      <c r="B232" s="33" t="s">
+      <c r="B232" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C232" s="50">
@@ -12650,29 +12945,35 @@
       <c r="E232" s="13" t="s">
         <v>599</v>
       </c>
-      <c r="F232" s="41" t="s">
+      <c r="F232" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G232" s="51" t="s">
+      <c r="G232" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H232" s="16"/>
-      <c r="I232" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J232" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K232" s="16"/>
-      <c r="L232" s="38"/>
-      <c r="M232" s="20"/>
+      <c r="H232" s="64">
+        <v>39192</v>
+      </c>
+      <c r="I232" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J232" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K232" s="64"/>
+      <c r="L232" s="63" t="s">
+        <v>736</v>
+      </c>
+      <c r="M232" s="63" t="s">
+        <v>737</v>
+      </c>
       <c r="N232" s="7"/>
     </row>
     <row r="233" spans="1:14" ht="15.75">
       <c r="A233" s="14">
         <v>234</v>
       </c>
-      <c r="B233" s="33" t="s">
+      <c r="B233" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C233" s="50">
@@ -12684,29 +12985,35 @@
       <c r="E233" s="13" t="s">
         <v>578</v>
       </c>
-      <c r="F233" s="41" t="s">
+      <c r="F233" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G233" s="51" t="s">
+      <c r="G233" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H233" s="16"/>
-      <c r="I233" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J233" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K233" s="16"/>
-      <c r="L233" s="38"/>
-      <c r="M233" s="20"/>
+      <c r="H233" s="64">
+        <v>40266</v>
+      </c>
+      <c r="I233" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J233" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K233" s="64"/>
+      <c r="L233" s="63" t="s">
+        <v>688</v>
+      </c>
+      <c r="M233" s="63" t="s">
+        <v>689</v>
+      </c>
       <c r="N233" s="7"/>
     </row>
     <row r="234" spans="1:14" ht="15.75">
       <c r="A234" s="14">
         <v>235</v>
       </c>
-      <c r="B234" s="33" t="s">
+      <c r="B234" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C234" s="50">
@@ -12718,29 +13025,35 @@
       <c r="E234" s="13" t="s">
         <v>601</v>
       </c>
-      <c r="F234" s="41" t="s">
+      <c r="F234" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G234" s="51" t="s">
+      <c r="G234" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H234" s="16"/>
-      <c r="I234" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J234" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K234" s="16"/>
-      <c r="L234" s="38"/>
-      <c r="M234" s="20"/>
+      <c r="H234" s="64">
+        <v>40959</v>
+      </c>
+      <c r="I234" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J234" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K234" s="64"/>
+      <c r="L234" s="63" t="s">
+        <v>738</v>
+      </c>
+      <c r="M234" s="63" t="s">
+        <v>739</v>
+      </c>
       <c r="N234" s="7"/>
     </row>
     <row r="235" spans="1:14" ht="15.75">
       <c r="A235" s="14">
         <v>236</v>
       </c>
-      <c r="B235" s="33" t="s">
+      <c r="B235" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C235" s="50">
@@ -12752,29 +13065,35 @@
       <c r="E235" s="13" t="s">
         <v>603</v>
       </c>
-      <c r="F235" s="41" t="s">
+      <c r="F235" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G235" s="51" t="s">
+      <c r="G235" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H235" s="16"/>
-      <c r="I235" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J235" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K235" s="16"/>
-      <c r="L235" s="38"/>
-      <c r="M235" s="14"/>
+      <c r="H235" s="64">
+        <v>40823</v>
+      </c>
+      <c r="I235" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J235" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K235" s="64"/>
+      <c r="L235" s="63" t="s">
+        <v>740</v>
+      </c>
+      <c r="M235" s="63" t="s">
+        <v>741</v>
+      </c>
       <c r="N235" s="7"/>
     </row>
     <row r="236" spans="1:14" ht="15.75">
       <c r="A236" s="14">
         <v>237</v>
       </c>
-      <c r="B236" s="33" t="s">
+      <c r="B236" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C236" s="50">
@@ -12786,29 +13105,35 @@
       <c r="E236" s="13" t="s">
         <v>603</v>
       </c>
-      <c r="F236" s="41" t="s">
+      <c r="F236" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G236" s="51" t="s">
+      <c r="G236" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H236" s="16"/>
-      <c r="I236" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J236" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K236" s="16"/>
-      <c r="L236" s="38"/>
-      <c r="M236" s="20"/>
+      <c r="H236" s="64">
+        <v>40536</v>
+      </c>
+      <c r="I236" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J236" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K236" s="64"/>
+      <c r="L236" s="63" t="s">
+        <v>740</v>
+      </c>
+      <c r="M236" s="63" t="s">
+        <v>741</v>
+      </c>
       <c r="N236" s="7"/>
     </row>
     <row r="237" spans="1:14" ht="15.75">
       <c r="A237" s="14">
         <v>238</v>
       </c>
-      <c r="B237" s="33" t="s">
+      <c r="B237" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C237" s="50">
@@ -12820,29 +13145,35 @@
       <c r="E237" s="13" t="s">
         <v>606</v>
       </c>
-      <c r="F237" s="41" t="s">
+      <c r="F237" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G237" s="51" t="s">
+      <c r="G237" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H237" s="16"/>
-      <c r="I237" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J237" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K237" s="16"/>
-      <c r="L237" s="38"/>
-      <c r="M237" s="20"/>
+      <c r="H237" s="64">
+        <v>39300</v>
+      </c>
+      <c r="I237" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J237" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K237" s="64"/>
+      <c r="L237" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="M237" s="63" t="s">
+        <v>376</v>
+      </c>
       <c r="N237" s="7"/>
     </row>
     <row r="238" spans="1:14" ht="15.75">
       <c r="A238" s="14">
         <v>239</v>
       </c>
-      <c r="B238" s="33" t="s">
+      <c r="B238" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C238" s="50"/>
@@ -12852,29 +13183,29 @@
       <c r="E238" s="13" t="s">
         <v>607</v>
       </c>
-      <c r="F238" s="41" t="s">
+      <c r="F238" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G238" s="51" t="s">
+      <c r="G238" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H238" s="16"/>
-      <c r="I238" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J238" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K238" s="16"/>
-      <c r="L238" s="38"/>
-      <c r="M238" s="20"/>
+      <c r="H238" s="64"/>
+      <c r="I238" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J238" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K238" s="64"/>
+      <c r="L238" s="63"/>
+      <c r="M238" s="63"/>
       <c r="N238" s="7"/>
     </row>
     <row r="239" spans="1:14" ht="15.75">
       <c r="A239" s="14">
         <v>240</v>
       </c>
-      <c r="B239" s="33" t="s">
+      <c r="B239" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C239" s="50">
@@ -12886,29 +13217,35 @@
       <c r="E239" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="F239" s="41" t="s">
+      <c r="F239" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G239" s="51" t="s">
+      <c r="G239" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H239" s="16"/>
-      <c r="I239" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J239" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K239" s="16"/>
-      <c r="L239" s="38"/>
-      <c r="M239" s="20"/>
+      <c r="H239" s="64">
+        <v>38939</v>
+      </c>
+      <c r="I239" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J239" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K239" s="64"/>
+      <c r="L239" s="63" t="s">
+        <v>407</v>
+      </c>
+      <c r="M239" s="63" t="s">
+        <v>408</v>
+      </c>
       <c r="N239" s="7"/>
     </row>
     <row r="240" spans="1:14" ht="15.75">
       <c r="A240" s="14">
         <v>241</v>
       </c>
-      <c r="B240" s="33" t="s">
+      <c r="B240" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C240" s="50">
@@ -12920,29 +13257,35 @@
       <c r="E240" s="13" t="s">
         <v>610</v>
       </c>
-      <c r="F240" s="41" t="s">
+      <c r="F240" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G240" s="51" t="s">
+      <c r="G240" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H240" s="16"/>
-      <c r="I240" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J240" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K240" s="16"/>
-      <c r="L240" s="38"/>
-      <c r="M240" s="21"/>
+      <c r="H240" s="64">
+        <v>40467</v>
+      </c>
+      <c r="I240" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J240" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K240" s="64"/>
+      <c r="L240" s="63" t="s">
+        <v>742</v>
+      </c>
+      <c r="M240" s="63" t="s">
+        <v>743</v>
+      </c>
       <c r="N240" s="7"/>
     </row>
     <row r="241" spans="1:14" ht="15.75">
       <c r="A241" s="14">
         <v>242</v>
       </c>
-      <c r="B241" s="33" t="s">
+      <c r="B241" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C241" s="50">
@@ -12954,29 +13297,35 @@
       <c r="E241" s="13" t="s">
         <v>612</v>
       </c>
-      <c r="F241" s="41" t="s">
+      <c r="F241" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G241" s="51" t="s">
+      <c r="G241" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H241" s="16"/>
-      <c r="I241" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J241" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K241" s="16"/>
-      <c r="L241" s="38"/>
-      <c r="M241" s="20"/>
+      <c r="H241" s="64">
+        <v>40467</v>
+      </c>
+      <c r="I241" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J241" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K241" s="64"/>
+      <c r="L241" s="63" t="s">
+        <v>744</v>
+      </c>
+      <c r="M241" s="63" t="s">
+        <v>745</v>
+      </c>
       <c r="N241" s="7"/>
     </row>
     <row r="242" spans="1:14" ht="15.75">
       <c r="A242" s="14">
         <v>243</v>
       </c>
-      <c r="B242" s="33" t="s">
+      <c r="B242" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C242" s="50">
@@ -12988,29 +13337,33 @@
       <c r="E242" s="13" t="s">
         <v>614</v>
       </c>
-      <c r="F242" s="41" t="s">
+      <c r="F242" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G242" s="51" t="s">
+      <c r="G242" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H242" s="16"/>
-      <c r="I242" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J242" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K242" s="16"/>
-      <c r="L242" s="38"/>
-      <c r="M242" s="20"/>
+      <c r="H242" s="64"/>
+      <c r="I242" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J242" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K242" s="64"/>
+      <c r="L242" s="63" t="s">
+        <v>746</v>
+      </c>
+      <c r="M242" s="63" t="s">
+        <v>433</v>
+      </c>
       <c r="N242" s="7"/>
     </row>
     <row r="243" spans="1:14" ht="15.75">
       <c r="A243" s="14">
         <v>244</v>
       </c>
-      <c r="B243" s="33" t="s">
+      <c r="B243" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C243" s="50">
@@ -13022,29 +13375,31 @@
       <c r="E243" s="13" t="s">
         <v>616</v>
       </c>
-      <c r="F243" s="41" t="s">
+      <c r="F243" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G243" s="51" t="s">
+      <c r="G243" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H243" s="16"/>
-      <c r="I243" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J243" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K243" s="16"/>
-      <c r="L243" s="38"/>
-      <c r="M243" s="14"/>
+      <c r="H243" s="64">
+        <v>40978</v>
+      </c>
+      <c r="I243" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J243" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K243" s="64"/>
+      <c r="L243" s="63"/>
+      <c r="M243" s="63"/>
       <c r="N243" s="7"/>
     </row>
     <row r="244" spans="1:14" ht="15.75">
       <c r="A244" s="14">
         <v>245</v>
       </c>
-      <c r="B244" s="33" t="s">
+      <c r="B244" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C244" s="50">
@@ -13056,61 +13411,69 @@
       <c r="E244" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="F244" s="41" t="s">
+      <c r="F244" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G244" s="51" t="s">
+      <c r="G244" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H244" s="16"/>
-      <c r="I244" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J244" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K244" s="16"/>
-      <c r="L244" s="38"/>
-      <c r="M244" s="7"/>
+      <c r="H244" s="64">
+        <v>40957</v>
+      </c>
+      <c r="I244" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J244" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K244" s="64"/>
+      <c r="L244" s="63" t="s">
+        <v>747</v>
+      </c>
+      <c r="M244" s="7" t="s">
+        <v>733</v>
+      </c>
       <c r="N244" s="7"/>
     </row>
     <row r="245" spans="1:14" ht="15.75">
       <c r="A245" s="14">
         <v>246</v>
       </c>
-      <c r="B245" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C245" s="50"/>
-      <c r="D245" s="51" t="s">
+      <c r="B245" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C245" s="50">
+        <v>738</v>
+      </c>
+      <c r="D245" s="63" t="s">
         <v>178</v>
       </c>
-      <c r="E245" s="51" t="s">
+      <c r="E245" s="63" t="s">
         <v>617</v>
       </c>
-      <c r="F245" s="41" t="s">
+      <c r="F245" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="G245" s="51" t="s">
+      <c r="G245" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H245" s="16"/>
-      <c r="I245" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J245" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K245" s="16"/>
-      <c r="L245" s="38"/>
-      <c r="M245" s="20"/>
+      <c r="H245" s="64"/>
+      <c r="I245" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J245" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K245" s="64"/>
+      <c r="L245" s="63"/>
+      <c r="M245" s="63"/>
       <c r="N245" s="7"/>
     </row>
     <row r="246" spans="1:14" ht="15.75">
       <c r="A246" s="14">
         <v>247</v>
       </c>
-      <c r="B246" s="33" t="s">
+      <c r="B246" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C246" s="50">
@@ -13122,267 +13485,307 @@
       <c r="E246" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="F246" s="51" t="s">
+      <c r="F246" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G246" s="51" t="s">
+      <c r="G246" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H246" s="16"/>
-      <c r="I246" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J246" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K246" s="16"/>
-      <c r="L246" s="38"/>
-      <c r="M246" s="21"/>
+      <c r="H246" s="64">
+        <v>40475</v>
+      </c>
+      <c r="I246" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J246" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K246" s="64"/>
+      <c r="L246" s="63" t="s">
+        <v>748</v>
+      </c>
+      <c r="M246" s="63" t="s">
+        <v>439</v>
+      </c>
       <c r="N246" s="7"/>
     </row>
     <row r="247" spans="1:14" ht="15.75">
       <c r="A247" s="14">
         <v>248</v>
       </c>
-      <c r="B247" s="33" t="s">
+      <c r="B247" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C247" s="50">
         <v>732</v>
       </c>
       <c r="D247" s="12" t="s">
-        <v>619</v>
+        <v>749</v>
       </c>
       <c r="E247" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="F247" s="51" t="s">
+      <c r="F247" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G247" s="51" t="s">
+      <c r="G247" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H247" s="16"/>
-      <c r="I247" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J247" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K247" s="16"/>
-      <c r="L247" s="38"/>
-      <c r="M247" s="20"/>
+      <c r="H247" s="64">
+        <v>39952</v>
+      </c>
+      <c r="I247" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J247" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K247" s="64"/>
+      <c r="L247" s="63" t="s">
+        <v>375</v>
+      </c>
+      <c r="M247" s="63" t="s">
+        <v>376</v>
+      </c>
       <c r="N247" s="7"/>
     </row>
     <row r="248" spans="1:14" ht="15.75">
       <c r="A248" s="14">
         <v>249</v>
       </c>
-      <c r="B248" s="33" t="s">
+      <c r="B248" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C248" s="50">
         <v>728</v>
       </c>
       <c r="D248" s="12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E248" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="F248" s="51" t="s">
+      <c r="F248" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G248" s="51" t="s">
+      <c r="G248" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H248" s="16"/>
-      <c r="I248" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J248" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K248" s="16"/>
-      <c r="L248" s="38"/>
-      <c r="M248" s="21"/>
+      <c r="H248" s="64">
+        <v>40606</v>
+      </c>
+      <c r="I248" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J248" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K248" s="64"/>
+      <c r="L248" s="63" t="s">
+        <v>750</v>
+      </c>
+      <c r="M248" s="63" t="s">
+        <v>751</v>
+      </c>
       <c r="N248" s="7"/>
     </row>
     <row r="249" spans="1:14" ht="15.75">
       <c r="A249" s="14">
         <v>250</v>
       </c>
-      <c r="B249" s="33" t="s">
+      <c r="B249" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C249" s="50">
         <v>760</v>
       </c>
       <c r="D249" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E249" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F249" s="51" t="s">
+      <c r="F249" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G249" s="51" t="s">
+      <c r="G249" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H249" s="16"/>
-      <c r="I249" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J249" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K249" s="16"/>
-      <c r="L249" s="7"/>
-      <c r="M249" s="20"/>
+      <c r="H249" s="64">
+        <v>41030</v>
+      </c>
+      <c r="I249" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J249" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K249" s="64"/>
+      <c r="L249" s="63" t="s">
+        <v>367</v>
+      </c>
+      <c r="M249" s="63" t="s">
+        <v>752</v>
+      </c>
       <c r="N249" s="7"/>
     </row>
     <row r="250" spans="1:14" ht="15.75">
       <c r="A250" s="14">
         <v>251</v>
       </c>
-      <c r="B250" s="33" t="s">
+      <c r="B250" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C250" s="50">
         <v>741</v>
       </c>
       <c r="D250" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E250" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="F250" s="51" t="s">
+      <c r="F250" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G250" s="51" t="s">
+      <c r="G250" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H250" s="16"/>
-      <c r="I250" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J250" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K250" s="16"/>
-      <c r="L250" s="7"/>
-      <c r="M250" s="28"/>
+      <c r="H250" s="64">
+        <v>40550</v>
+      </c>
+      <c r="I250" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J250" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K250" s="64"/>
+      <c r="L250" s="63" t="s">
+        <v>753</v>
+      </c>
+      <c r="M250" s="63"/>
       <c r="N250" s="7"/>
     </row>
     <row r="251" spans="1:14" ht="15.75">
       <c r="A251" s="14">
         <v>252</v>
       </c>
-      <c r="B251" s="33" t="s">
+      <c r="B251" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C251" s="50">
         <v>733</v>
       </c>
       <c r="D251" s="24" t="s">
+        <v>622</v>
+      </c>
+      <c r="E251" s="25" t="s">
         <v>623</v>
       </c>
-      <c r="E251" s="25" t="s">
-        <v>624</v>
-      </c>
-      <c r="F251" s="51" t="s">
+      <c r="F251" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G251" s="51" t="s">
+      <c r="G251" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H251" s="16"/>
-      <c r="I251" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J251" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K251" s="16"/>
+      <c r="H251" s="64"/>
+      <c r="I251" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J251" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K251" s="64"/>
       <c r="L251" s="7"/>
-      <c r="M251" s="21"/>
+      <c r="M251" s="63"/>
       <c r="N251" s="7"/>
     </row>
     <row r="252" spans="1:14" ht="15.75">
       <c r="A252" s="14">
         <v>253</v>
       </c>
-      <c r="B252" s="33" t="s">
+      <c r="B252" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C252" s="50">
         <v>744</v>
       </c>
-      <c r="D252" s="51" t="s">
+      <c r="D252" s="63" t="s">
+        <v>624</v>
+      </c>
+      <c r="E252" s="63" t="s">
         <v>625</v>
       </c>
-      <c r="E252" s="51" t="s">
-        <v>626</v>
-      </c>
-      <c r="F252" s="51" t="s">
+      <c r="F252" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G252" s="51" t="s">
+      <c r="G252" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H252" s="16"/>
-      <c r="I252" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J252" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K252" s="16"/>
-      <c r="L252" s="7"/>
-      <c r="M252" s="14"/>
+      <c r="H252" s="64">
+        <v>41105</v>
+      </c>
+      <c r="I252" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J252" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K252" s="64"/>
+      <c r="L252" s="63" t="s">
+        <v>420</v>
+      </c>
+      <c r="M252" s="63" t="s">
+        <v>419</v>
+      </c>
       <c r="N252" s="7"/>
     </row>
     <row r="253" spans="1:14" ht="15.75">
       <c r="A253" s="14">
         <v>254</v>
       </c>
-      <c r="B253" s="33" t="s">
+      <c r="B253" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C253" s="50">
         <v>850</v>
       </c>
       <c r="D253" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E253" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="F253" s="51" t="s">
+      <c r="F253" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G253" s="51" t="s">
+      <c r="G253" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H253" s="16"/>
-      <c r="I253" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J253" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K253" s="16"/>
-      <c r="L253" s="7"/>
-      <c r="M253" s="21"/>
+      <c r="H253" s="64">
+        <v>40425</v>
+      </c>
+      <c r="I253" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J253" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K253" s="64"/>
+      <c r="L253" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="M253" s="63" t="s">
+        <v>755</v>
+      </c>
       <c r="N253" s="7"/>
     </row>
     <row r="254" spans="1:14" ht="15.75">
       <c r="A254" s="14">
         <v>255</v>
       </c>
-      <c r="B254" s="33" t="s">
+      <c r="B254" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C254" s="52">
@@ -13394,20 +13797,20 @@
       <c r="E254" s="52" t="s">
         <v>322</v>
       </c>
-      <c r="F254" s="51" t="s">
+      <c r="F254" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G254" s="51" t="s">
+      <c r="G254" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H254" s="16"/>
-      <c r="I254" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J254" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K254" s="16"/>
+      <c r="H254" s="64"/>
+      <c r="I254" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J254" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K254" s="64"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
       <c r="N254" s="7"/>
@@ -13416,170 +13819,198 @@
       <c r="A255" s="14">
         <v>256</v>
       </c>
-      <c r="B255" s="33" t="s">
+      <c r="B255" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C255" s="52">
         <v>875</v>
       </c>
       <c r="D255" s="52" t="s">
+        <v>627</v>
+      </c>
+      <c r="E255" s="52" t="s">
         <v>628</v>
       </c>
-      <c r="E255" s="52" t="s">
-        <v>629</v>
-      </c>
-      <c r="F255" s="51" t="s">
+      <c r="F255" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G255" s="51" t="s">
+      <c r="G255" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H255" s="16"/>
-      <c r="I255" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J255" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K255" s="16"/>
-      <c r="L255" s="7"/>
-      <c r="M255" s="14"/>
+      <c r="H255" s="64">
+        <v>40452</v>
+      </c>
+      <c r="I255" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J255" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K255" s="64"/>
+      <c r="L255" s="7" t="s">
+        <v>716</v>
+      </c>
+      <c r="M255" s="63" t="s">
+        <v>717</v>
+      </c>
       <c r="N255" s="7"/>
     </row>
     <row r="256" spans="1:14" ht="15.75">
       <c r="A256" s="14">
         <v>257</v>
       </c>
-      <c r="B256" s="33" t="s">
+      <c r="B256" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C256" s="52">
         <v>727</v>
       </c>
       <c r="D256" s="52" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E256" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="F256" s="51" t="s">
+      <c r="F256" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G256" s="51" t="s">
+      <c r="G256" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H256" s="16"/>
-      <c r="I256" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J256" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K256" s="16"/>
-      <c r="L256" s="7"/>
-      <c r="M256" s="20"/>
+      <c r="H256" s="64">
+        <v>40386</v>
+      </c>
+      <c r="I256" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J256" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K256" s="64"/>
+      <c r="L256" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="M256" s="63" t="s">
+        <v>278</v>
+      </c>
       <c r="N256" s="7"/>
     </row>
     <row r="257" spans="1:16" ht="15.75">
       <c r="A257" s="14">
         <v>258</v>
       </c>
-      <c r="B257" s="33" t="s">
+      <c r="B257" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C257" s="52">
         <v>880</v>
       </c>
       <c r="D257" s="52" t="s">
+        <v>630</v>
+      </c>
+      <c r="E257" s="52" t="s">
         <v>631</v>
       </c>
-      <c r="E257" s="52" t="s">
-        <v>632</v>
-      </c>
-      <c r="F257" s="51" t="s">
+      <c r="F257" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G257" s="51" t="s">
+      <c r="G257" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H257" s="16"/>
-      <c r="I257" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J257" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K257" s="16"/>
-      <c r="L257" s="7"/>
-      <c r="M257" s="14"/>
+      <c r="H257" s="64">
+        <v>40877</v>
+      </c>
+      <c r="I257" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J257" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K257" s="64"/>
+      <c r="L257" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="M257" s="63"/>
       <c r="N257" s="7"/>
     </row>
     <row r="258" spans="1:16" ht="15.75">
       <c r="A258" s="14">
         <v>259</v>
       </c>
-      <c r="B258" s="33" t="s">
+      <c r="B258" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C258" s="52">
         <v>777</v>
       </c>
       <c r="D258" s="52" t="s">
+        <v>632</v>
+      </c>
+      <c r="E258" s="52" t="s">
         <v>633</v>
       </c>
-      <c r="E258" s="52" t="s">
-        <v>634</v>
-      </c>
-      <c r="F258" s="51" t="s">
+      <c r="F258" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G258" s="51" t="s">
+      <c r="G258" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H258" s="16"/>
-      <c r="I258" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J258" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K258" s="16"/>
-      <c r="L258" s="7"/>
-      <c r="M258" s="20"/>
+      <c r="H258" s="64">
+        <v>40546</v>
+      </c>
+      <c r="I258" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J258" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K258" s="64"/>
+      <c r="L258" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="M258" s="63" t="s">
+        <v>758</v>
+      </c>
       <c r="N258" s="7"/>
     </row>
     <row r="259" spans="1:16" ht="15.75">
       <c r="A259" s="14">
         <v>260</v>
       </c>
-      <c r="B259" s="33" t="s">
+      <c r="B259" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C259" s="52">
         <v>873</v>
       </c>
       <c r="D259" s="52" t="s">
+        <v>634</v>
+      </c>
+      <c r="E259" s="52" t="s">
         <v>635</v>
       </c>
-      <c r="E259" s="52" t="s">
-        <v>636</v>
-      </c>
-      <c r="F259" s="51" t="s">
+      <c r="F259" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G259" s="51" t="s">
+      <c r="G259" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H259" s="16"/>
-      <c r="I259" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J259" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K259" s="16"/>
-      <c r="L259" s="7"/>
-      <c r="M259" s="20"/>
+      <c r="H259" s="64">
+        <v>40467</v>
+      </c>
+      <c r="I259" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J259" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K259" s="64"/>
+      <c r="L259" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="M259" s="63" t="s">
+        <v>760</v>
+      </c>
       <c r="N259" s="7"/>
       <c r="P259" s="32"/>
     </row>
@@ -13587,170 +14018,194 @@
       <c r="A260" s="14">
         <v>261</v>
       </c>
-      <c r="B260" s="33" t="s">
+      <c r="B260" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C260" s="52">
         <v>909</v>
       </c>
       <c r="D260" s="52" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E260" s="52" t="s">
         <v>274</v>
       </c>
-      <c r="F260" s="51" t="s">
+      <c r="F260" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G260" s="51" t="s">
+      <c r="G260" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H260" s="16"/>
-      <c r="I260" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J260" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K260" s="16"/>
-      <c r="L260" s="7"/>
-      <c r="M260" s="20"/>
+      <c r="H260" s="64">
+        <v>40763</v>
+      </c>
+      <c r="I260" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J260" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K260" s="64"/>
+      <c r="L260" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="M260" s="63" t="s">
+        <v>762</v>
+      </c>
       <c r="N260" s="7"/>
     </row>
     <row r="261" spans="1:16" ht="15.75">
       <c r="A261" s="14">
         <v>262</v>
       </c>
-      <c r="B261" s="33" t="s">
+      <c r="B261" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C261" s="52">
         <v>854</v>
       </c>
       <c r="D261" s="52" t="s">
+        <v>637</v>
+      </c>
+      <c r="E261" s="52" t="s">
         <v>638</v>
       </c>
-      <c r="E261" s="52" t="s">
-        <v>639</v>
-      </c>
-      <c r="F261" s="51" t="s">
+      <c r="F261" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G261" s="51" t="s">
+      <c r="G261" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H261" s="16"/>
-      <c r="I261" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J261" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K261" s="16"/>
+      <c r="H261" s="64"/>
+      <c r="I261" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J261" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K261" s="64"/>
       <c r="L261" s="7"/>
-      <c r="M261" s="20"/>
+      <c r="M261" s="63"/>
       <c r="N261" s="7"/>
     </row>
     <row r="262" spans="1:16" ht="15.75">
       <c r="A262" s="14">
         <v>263</v>
       </c>
-      <c r="B262" s="33" t="s">
+      <c r="B262" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C262" s="52">
         <v>863</v>
       </c>
       <c r="D262" s="52" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E262" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="F262" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="F262" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G262" s="51" t="s">
+      <c r="G262" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H262" s="16"/>
-      <c r="I262" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J262" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K262" s="16"/>
-      <c r="L262" s="7"/>
-      <c r="M262" s="14"/>
-      <c r="N262" s="14"/>
+      <c r="H262" s="64">
+        <v>40941</v>
+      </c>
+      <c r="I262" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J262" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K262" s="64"/>
+      <c r="L262" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="M262" s="63" t="s">
+        <v>461</v>
+      </c>
+      <c r="N262" s="63"/>
     </row>
     <row r="263" spans="1:16" ht="15.75">
       <c r="A263" s="14">
         <v>264</v>
       </c>
-      <c r="B263" s="33" t="s">
+      <c r="B263" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C263" s="55">
         <v>902</v>
       </c>
       <c r="D263" s="55" t="s">
+        <v>640</v>
+      </c>
+      <c r="E263" s="55" t="s">
         <v>641</v>
       </c>
-      <c r="E263" s="55" t="s">
-        <v>642</v>
-      </c>
-      <c r="F263" s="51" t="s">
+      <c r="F263" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G263" s="51" t="s">
+      <c r="G263" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H263" s="16"/>
-      <c r="I263" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J263" s="33" t="s">
-        <v>118</v>
-      </c>
-      <c r="K263" s="16"/>
-      <c r="L263" s="7"/>
-      <c r="M263" s="14"/>
-      <c r="N263" s="14"/>
+      <c r="H263" s="64">
+        <v>40766</v>
+      </c>
+      <c r="I263" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J263" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="K263" s="64"/>
+      <c r="L263" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="M263" s="63" t="s">
+        <v>764</v>
+      </c>
+      <c r="N263" s="63"/>
     </row>
     <row r="264" spans="1:16" ht="15.75">
       <c r="A264" s="14">
         <v>265</v>
       </c>
-      <c r="B264" s="33" t="s">
+      <c r="B264" s="63" t="s">
         <v>18</v>
       </c>
       <c r="C264" s="52">
         <v>886</v>
       </c>
       <c r="D264" s="52" t="s">
+        <v>642</v>
+      </c>
+      <c r="E264" s="52" t="s">
         <v>643</v>
       </c>
-      <c r="E264" s="52" t="s">
-        <v>644</v>
-      </c>
-      <c r="F264" s="51" t="s">
+      <c r="F264" s="63" t="s">
         <v>56</v>
       </c>
-      <c r="G264" s="51" t="s">
+      <c r="G264" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="H264" s="16"/>
-      <c r="I264" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="J264" s="33" t="s">
+      <c r="H264" s="64">
+        <v>40934</v>
+      </c>
+      <c r="I264" s="65" t="s">
+        <v>117</v>
+      </c>
+      <c r="J264" s="63" t="s">
         <v>118</v>
       </c>
       <c r="K264" s="5"/>
-      <c r="L264" s="7"/>
-      <c r="M264" s="7"/>
+      <c r="L264" s="66" t="s">
+        <v>765</v>
+      </c>
+      <c r="M264" s="7" t="s">
+        <v>766</v>
+      </c>
       <c r="N264" s="7"/>
     </row>
     <row r="265" spans="1:16" ht="15.75">
@@ -13821,88 +14276,94 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <phoneticPr fontId="30" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <conditionalFormatting sqref="C53:C81">
-    <cfRule type="duplicateValues" dxfId="29" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C106">
-    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C107">
-    <cfRule type="duplicateValues" dxfId="27" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C108:C140">
-    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C141:C165">
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C176:C203">
-    <cfRule type="duplicateValues" dxfId="24" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="73"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C204:C205">
-    <cfRule type="duplicateValues" dxfId="23" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C266:C268">
+    <cfRule type="duplicateValues" dxfId="24" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C266:C1048576 C1:C175">
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D176:D203">
+    <cfRule type="duplicateValues" dxfId="22" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L153">
+    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L215">
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L216:L222 L125:L152 L1:L123 L154:L166 L168:L214 L265:L1048576">
+    <cfRule type="duplicateValues" dxfId="19" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M47">
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M145">
+    <cfRule type="duplicateValues" dxfId="17" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M190">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M205">
+    <cfRule type="duplicateValues" dxfId="15" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M206:M214 M120:M126 M138:M139 M141:M144 M154 M156 M128:M136 M160:M189 M146:M151 M191:M204 M216:M220 M222 M1:M46 M48:M117 M265:M1048576">
+    <cfRule type="duplicateValues" dxfId="14" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M215">
+    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M221">
+    <cfRule type="duplicateValues" dxfId="12" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C223:C237">
-    <cfRule type="duplicateValues" dxfId="22" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C238">
-    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C239:C244">
-    <cfRule type="duplicateValues" dxfId="18" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C245">
-    <cfRule type="duplicateValues" dxfId="17" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C246:C252">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C253">
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C266:C268">
-    <cfRule type="duplicateValues" dxfId="12" priority="36"/>
+  <conditionalFormatting sqref="L223:L264">
+    <cfRule type="duplicateValues" dxfId="1" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C266:C1048576 C1:C175">
-    <cfRule type="duplicateValues" dxfId="11" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D176:D203">
-    <cfRule type="duplicateValues" dxfId="10" priority="63"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L153">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L215">
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L216:L1048576 L125:L152 L1:L123 L154:L166 L168:L214">
-    <cfRule type="duplicateValues" dxfId="7" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M47">
-    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M145">
-    <cfRule type="duplicateValues" dxfId="5" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M190">
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M205">
-    <cfRule type="duplicateValues" dxfId="3" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M206:M214 M120:M126 M138:M139 M141:M144 M154 M156 M128:M136 M160:M189 M146:M151 M191:M204 M216:M220 M222:M1048576 M1:M46 M48:M117">
-    <cfRule type="duplicateValues" dxfId="2" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M215">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M221">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="M223:M264">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.75" header="0.2" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>
